--- a/templates/_masters/REV-005-holiday-event-pricing-calendar-BLANK.xlsx
+++ b/templates/_masters/REV-005-holiday-event-pricing-calendar-BLANK.xlsx
@@ -557,7 +557,7 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00FFB3B3"/>
+          <fgColor rgb="00FFCCCC"/>
         </patternFill>
       </fill>
     </dxf>
